--- a/Semaglutide2016.xlsx
+++ b/Semaglutide2016.xlsx
@@ -448,20 +448,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>浏览量</t>
+          <t>话题标签</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>话题标签</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>关键词</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>链接</t>
         </is>
@@ -498,18 +493,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>https://x.com/ClarivateHealth/status/765881217124278272</t>
         </is>
@@ -547,18 +536,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>https://x.com/FiercePharma/status/765937995245420545</t>
         </is>
@@ -595,18 +578,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>https://x.com/danvantri/status/765940043525525504</t>
         </is>
@@ -648,20 +625,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#pharma #marketing</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>#pharma #marketing</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>https://x.com/CarlyHFierce/status/765978764010414080</t>
         </is>
@@ -698,18 +670,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>https://x.com/mbotana/status/774488699539189760</t>
         </is>
@@ -748,20 +714,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016http</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>#EASD2016http</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>https://x.com/medpagetoday/status/774699000414949376</t>
         </is>
@@ -801,20 +762,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#SUSTAIN #EASD2016 #diabetes #cardiovascular #semaglutidehttp</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>#SUSTAIN #EASD2016 #diabetes #cardiovascular #semaglutidehttp</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
         <is>
           <t>https://x.com/GPacyk/status/774833749179633664</t>
         </is>
@@ -851,18 +807,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
         <is>
           <t>https://x.com/VikasReports/status/775513914339651586</t>
         </is>
@@ -899,18 +849,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
         <is>
           <t>https://x.com/M3_Europe/status/775639360154796032</t>
         </is>
@@ -949,20 +893,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#followback</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>#followback</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>https://x.com/AddonsBrowsers/status/775721299008032768</t>
         </is>
@@ -1001,20 +940,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
         <is>
           <t>https://x.com/DrTinahones/status/776343533028540416</t>
         </is>
@@ -1053,20 +987,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016Semaglutide</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>#EASD2016Semaglutide</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
         <is>
           <t>https://x.com/endocrine_ali/status/776344842758680576</t>
         </is>
@@ -1105,20 +1034,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
         <is>
           <t>https://x.com/SEDiabetes/status/776347769963442176</t>
         </is>
@@ -1157,20 +1081,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
         <is>
           <t>https://x.com/cristinatejerap/status/776348082602668032</t>
         </is>
@@ -1209,20 +1128,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
         <is>
           <t>https://x.com/DrTinahones/status/776348738335965184</t>
         </is>
@@ -1263,20 +1177,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
         <is>
           <t>https://x.com/Alz_Gal/status/776349001067167744</t>
         </is>
@@ -1315,20 +1224,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
         <is>
           <t>https://x.com/DrTinahones/status/776351199822024704</t>
         </is>
@@ -1367,20 +1271,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
         <is>
           <t>https://x.com/cristinatejerap/status/776352252739092480</t>
         </is>
@@ -1419,20 +1318,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
         <is>
           <t>https://x.com/SEDiabetes/status/776352817472737280</t>
         </is>
@@ -1474,20 +1368,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
         <is>
           <t>https://x.com/DesChatterjee/status/776353466931417088</t>
         </is>
@@ -1529,20 +1418,15 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
         <is>
           <t>https://x.com/DesChatterjee/status/776353469536079872</t>
         </is>
@@ -1582,20 +1466,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#SEMAGLUTIDE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>#SEMAGLUTIDE</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
         <is>
           <t>https://x.com/CristobMorales/status/776426490586075136</t>
         </is>
@@ -1632,18 +1511,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
         <is>
           <t>https://x.com/CristobMorales/status/776428902596116480</t>
         </is>
@@ -1682,20 +1555,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
         <is>
           <t>https://x.com/cristinatejerap/status/776645708682235904</t>
         </is>
@@ -1732,18 +1600,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
         <is>
           <t>https://x.com/APMinfos/status/776670136153628672</t>
         </is>
@@ -1782,20 +1644,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#dkbiz</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>#dkbiz</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
         <is>
           <t>https://x.com/LasseLadefoged/status/776670160740548608</t>
         </is>
@@ -1834,20 +1691,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
         <is>
           <t>https://x.com/NEJM/status/776670757762072576</t>
         </is>
@@ -1886,20 +1738,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#easd2016http</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>#easd2016http</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
         <is>
           <t>https://x.com/CristobMorales/status/776671650892873728</t>
         </is>
@@ -1940,20 +1787,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Semaglutide #cardiovascular #diabetes #heartdisease</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>#Semaglutide #cardiovascular #diabetes #heartdisease</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
         <is>
           <t>https://x.com/MedWatchNews/status/776672396329779200</t>
         </is>
@@ -1995,20 +1837,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASDSEMAGLUTIDE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>#EASDSEMAGLUTIDE</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
         <is>
           <t>https://x.com/CristobMorales/status/776672830553518080</t>
         </is>
@@ -2048,20 +1885,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD16semaglutide</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>#EASD16semaglutide</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
         <is>
           <t>https://x.com/cristinatejerap/status/776673283710353408</t>
         </is>
@@ -2100,20 +1932,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#semaglutide #Sustain #EASD2016</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>#semaglutide #Sustain #EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
         <is>
           <t>https://x.com/AliceYYCheng/status/776674202699100160</t>
         </is>
@@ -2152,20 +1979,15 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016 #SUSTAIN6</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>#EASD2016 #SUSTAIN6</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
         <is>
           <t>https://x.com/dr_kevinlee/status/776674225419587584</t>
         </is>
@@ -2204,20 +2026,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#SUSTAIN6 #EASD2016</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>#SUSTAIN6 #EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
         <is>
           <t>https://x.com/dcarbohydrated/status/776674850282803202</t>
         </is>
@@ -2257,18 +2074,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
         <is>
           <t>https://x.com/CristobMorales/status/776675510411755520</t>
         </is>
@@ -2307,20 +2118,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Novo</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>#Novo</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
         <is>
           <t>https://x.com/reutersBenHir/status/776676352569335808</t>
         </is>
@@ -2359,20 +2165,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
         <is>
           <t>https://x.com/DrTinahones/status/776676836298326016</t>
         </is>
@@ -2411,20 +2212,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016 #sustain</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>#EASD2016 #sustain</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
         <is>
           <t>https://x.com/cristinatejerap/status/776677014136877056</t>
         </is>
@@ -2461,18 +2257,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
         <is>
           <t>https://x.com/DrTinahones/status/776677615436492800</t>
         </is>
@@ -2511,20 +2301,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#share</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>#share</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
         <is>
           <t>https://x.com/Finwire/status/776677853328994304</t>
         </is>
@@ -2565,20 +2350,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#easd2016semaglutide</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>#easd2016semaglutide</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
         <is>
           <t>https://x.com/alejoromanmd/status/776678405060173825</t>
         </is>
@@ -2615,18 +2395,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
         <is>
           <t>https://x.com/Reuters_Health/status/776678435032793089</t>
         </is>
@@ -2666,20 +2440,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#semaglutide #SUSTAIN6 #EASD2016</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>#semaglutide #SUSTAIN6 #EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
         <is>
           <t>https://x.com/SisSkovsoe/status/776678458881630208</t>
         </is>
@@ -2718,20 +2487,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Semaglutide #EASD2016</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>#Semaglutide #EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
         <is>
           <t>https://x.com/AliceYYCheng/status/776678523633270784</t>
         </is>
@@ -2770,20 +2534,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016semaglutide</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>#EASD2016semaglutide</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
         <is>
           <t>https://x.com/alejoromanmd/status/776679253509275648</t>
         </is>
@@ -2822,20 +2581,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Semaglutide #SUSTAIN #EASD2016</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>#Semaglutide #SUSTAIN #EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
         <is>
           <t>https://x.com/AliceYYCheng/status/776679960970788869</t>
         </is>
@@ -2874,20 +2628,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#SUSTAIN6 #EASD2016</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>#SUSTAIN6 #EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
         <is>
           <t>https://x.com/dcarbohydrated/status/776680915875532800</t>
         </is>
@@ -2926,20 +2675,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#T2DM #EASD2016http</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>#T2DM #EASD2016http</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
         <is>
           <t>https://x.com/dr_kevinlee/status/776681202770141184</t>
         </is>
@@ -2980,20 +2724,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016 #SUSTAIN6 #retinopathy #NNH</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>#EASD2016 #SUSTAIN6 #retinopathy #NNH</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
         <is>
           <t>https://x.com/dr_kevinlee/status/776683384236044288</t>
         </is>
@@ -3030,18 +2769,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
         <is>
           <t>https://x.com/DrTinahones/status/776684118100836352</t>
         </is>
@@ -3079,18 +2812,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
         <is>
           <t>https://x.com/DrTinahones/status/776685313703964672</t>
         </is>
@@ -3127,18 +2854,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
         <is>
           <t>https://x.com/JuthiRoy07/status/776685940492242944</t>
         </is>
@@ -3177,20 +2898,15 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#SUSTAIN6 #EASD2016</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>#SUSTAIN6 #EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
         <is>
           <t>https://x.com/brendonneuen/status/776693678932758528</t>
         </is>
@@ -3231,20 +2947,15 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#easd2016http #SUSTAIN6</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>#easd2016http #SUSTAIN6</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
         <is>
           <t>https://x.com/CristobMorales/status/776696437228929024</t>
         </is>
@@ -3283,20 +2994,15 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
         <is>
           <t>https://x.com/fwpharma/status/776714190446858240</t>
         </is>
@@ -3333,18 +3039,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
         <is>
           <t>https://x.com/DrHubaEvaluator/status/776715389774471168</t>
         </is>
@@ -3387,20 +3087,15 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#easd2016</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>#easd2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
         <is>
           <t>https://x.com/clinthe/status/776716270473449472</t>
         </is>
@@ -3437,18 +3132,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
         <is>
           <t>https://x.com/RpratleyMD/status/776723840579866624</t>
         </is>
@@ -3485,18 +3174,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
         <is>
           <t>https://x.com/skathire/status/776725724849926144</t>
         </is>
@@ -3535,20 +3218,15 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Semaglutide #CV #GLP #heartdisease #weightloss #T2D</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>#Semaglutide #CV #GLP #heartdisease #weightloss #T2D</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
         <is>
           <t>https://x.com/DanielJDrucker/status/776725780025974784</t>
         </is>
@@ -3589,20 +3267,15 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Diabetes</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>#Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
         <is>
           <t>https://x.com/DanielJDrucker/status/776727476236148736</t>
         </is>
@@ -3639,18 +3312,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
         <is>
           <t>https://x.com/NatRevCardiol/status/776733414087127040</t>
         </is>
@@ -3687,18 +3354,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
         <is>
           <t>https://x.com/JuthiRoy07/status/776734028930035712</t>
         </is>
@@ -3739,20 +3400,15 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Semaglutide #diabetes #Victoza #Jardiance #EASD2016 #cvrisk</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>#Semaglutide #diabetes #Victoza #Jardiance #EASD2016 #cvrisk</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
         <is>
           <t>https://x.com/EdwMD/status/776735400282947584</t>
         </is>
@@ -3791,18 +3447,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
         <is>
           <t>https://x.com/FierceBiotech/status/776741611409661952</t>
         </is>
@@ -3839,18 +3489,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
         <is>
           <t>https://x.com/estebanjodar/status/776743290968375296</t>
         </is>
@@ -3887,18 +3531,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
         <is>
           <t>https://x.com/timohiltonjones/status/776745279097745408</t>
         </is>
@@ -3938,20 +3576,15 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
         <is>
           <t>https://x.com/FiercePharma/status/776746709313544192</t>
         </is>
@@ -3990,20 +3623,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Novo #diabetes #semaglutide</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>#Novo #diabetes #semaglutide</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
         <is>
           <t>https://x.com/reutersBenHir/status/776751993855549440</t>
         </is>
@@ -4043,20 +3671,15 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#semaglutide #SUSTAIN6 #cardiovascular</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>#semaglutide #SUSTAIN6 #cardiovascular</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
         <is>
           <t>https://x.com/DanielJDrucker/status/776759235971575808</t>
         </is>
@@ -4095,20 +3718,15 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Novo</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>#Novo</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
         <is>
           <t>https://x.com/TrecentoAM/status/776765038795300864</t>
         </is>
@@ -4147,18 +3765,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
         <is>
           <t>https://x.com/hmkyale/status/776768869998403585</t>
         </is>
@@ -4200,20 +3812,15 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#SUSTAIN6 #EASD2016 #Nephpearls</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>#SUSTAIN6 #EASD2016 #Nephpearls</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
         <is>
           <t>https://x.com/edgarvlermamd/status/776774133455532036</t>
         </is>
@@ -4252,20 +3859,15 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>#EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
         <is>
           <t>https://x.com/AJMC_Journal/status/776782958103408640</t>
         </is>
@@ -4307,20 +3909,15 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#2016EASD #Semaglutide #Cardiovascular #Diabetes</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>#2016EASD #Semaglutide #Cardiovascular #Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
         <is>
           <t>https://x.com/redGDPS/status/776803278881423361</t>
         </is>
@@ -4359,20 +3956,15 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EADS2016</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>#EADS2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
         <is>
           <t>https://x.com/jdflaysakier/status/776809819223252993</t>
         </is>
@@ -4411,20 +4003,15 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#TP</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>#TP</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
         <is>
           <t>https://x.com/jdflaysakier/status/776810628103204868</t>
         </is>
@@ -4463,18 +4050,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
         <is>
           <t>https://x.com/DrTinahones/status/776823824729923584</t>
         </is>
@@ -4513,20 +4094,15 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Cardiologyhttp</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>#Cardiologyhttp</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
         <is>
           <t>https://x.com/induscard/status/776828767247470592</t>
         </is>
@@ -4563,18 +4139,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
         <is>
           <t>https://x.com/ethanjweiss/status/776834895226122240</t>
         </is>
@@ -4616,20 +4186,15 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#figures</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>#figures</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
         <is>
           <t>https://x.com/ValleAlfonso/status/776862995678978048</t>
         </is>
@@ -4666,18 +4231,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
         <is>
           <t>https://x.com/TCTMD/status/776873833366028288</t>
         </is>
@@ -4716,20 +4275,15 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#cvMetabolic</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>#cvMetabolic</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
         <is>
           <t>https://x.com/ACCinTouch/status/776878372408418305</t>
         </is>
@@ -4766,18 +4320,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
         <is>
           <t>https://x.com/jdflaysakier/status/776908975656894464</t>
         </is>
@@ -4814,18 +4362,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
         <is>
           <t>https://x.com/MDMichael13/status/776939722006405120</t>
         </is>
@@ -4862,18 +4404,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
         <is>
           <t>https://x.com/LuisZuritaG/status/776986001453490177</t>
         </is>
@@ -4910,18 +4446,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
         <is>
           <t>https://x.com/stnolito/status/776997334941130752</t>
         </is>
@@ -4963,20 +4493,15 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Diabetes #Semaglutide #EASD2016</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>#Diabetes #Semaglutide #EASD2016</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
         <is>
           <t>https://x.com/dr_guevara/status/777036158983401472</t>
         </is>
@@ -5013,18 +4538,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
         <is>
           <t>https://x.com/srdeleiras/status/777074485648326656</t>
         </is>
@@ -5063,20 +4582,15 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Semaglutide #SUSTAIN6 #T2D</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>#Semaglutide #SUSTAIN6 #T2D</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
         <is>
           <t>https://x.com/DanielJDrucker/status/777076620754550784</t>
         </is>
@@ -5115,20 +4629,15 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#biotech</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>#biotech</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
         <is>
           <t>https://x.com/tom_biotech/status/777091772048605184</t>
         </is>
@@ -5165,18 +4674,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
         <is>
           <t>https://x.com/Diabetescouk/status/777146113321074688</t>
         </is>
@@ -5213,18 +4716,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
         <is>
           <t>https://x.com/ditogomez/status/777210809009205248</t>
         </is>
@@ -5263,20 +4760,15 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Semaglutide #diabetes</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>#Semaglutide #diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
         <is>
           <t>https://x.com/redGDPS/status/777551336346910721</t>
         </is>
@@ -5315,20 +4807,15 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Semaglutide #Cardiovascular #Diabetes</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>#Semaglutide #Cardiovascular #Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
         <is>
           <t>https://x.com/redGDPS/status/777551788685791232</t>
         </is>
@@ -5367,20 +4854,15 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#sémaglutide</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>#sémaglutide</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
         <is>
           <t>https://x.com/CardioOnline/status/777562169214984192</t>
         </is>
@@ -5419,20 +4901,15 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#DragiWebdo</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>#DragiWebdo</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
         <is>
           <t>https://x.com/Dr_Agibus/status/777597556712992768</t>
         </is>
@@ -5471,20 +4948,15 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#cardiovascular #MediaSoft</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>#cardiovascular #MediaSoft</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
         <is>
           <t>https://x.com/Sales_Vision/status/777774247066345472</t>
         </is>
@@ -5521,18 +4993,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
         <is>
           <t>https://x.com/EnzoCalamo/status/777781296936476672</t>
         </is>
@@ -5572,20 +5038,15 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD2016 #diabetes</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>#EASD2016 #diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
         <is>
           <t>https://x.com/LucieLEllis/status/777781946009128960</t>
         </is>
@@ -5622,18 +5083,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
         <is>
           <t>https://x.com/MedicalEmperor/status/777792665979084800</t>
         </is>
@@ -5672,20 +5127,15 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#diabetes #diabetic</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>#diabetes #diabetic</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
         <is>
           <t>https://x.com/Prikkedief/status/777800281627123712</t>
         </is>
@@ -5724,20 +5174,15 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#cardiology #heart</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>#cardiology #heart</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
         <is>
           <t>https://x.com/CardioResearch/status/777800297758416896</t>
         </is>
@@ -5774,18 +5219,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
         <is>
           <t>https://x.com/ASNKidney/status/777839773935407104</t>
         </is>
@@ -5824,20 +5263,15 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#diabetes #Heart</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>#diabetes #Heart</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
         <is>
           <t>https://x.com/HeartOTXHeartMD/status/777880538002497540</t>
         </is>
@@ -5874,18 +5308,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
         <is>
           <t>https://x.com/DrSharma/status/777891056344002560</t>
         </is>
@@ -5922,18 +5350,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
         <is>
           <t>https://x.com/dremarquezr/status/777913890927546368</t>
         </is>
@@ -5972,20 +5394,15 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#diabetes #researchhttp</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>#diabetes #researchhttp</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
         <is>
           <t>https://x.com/AFMResearch/status/778657150906298368</t>
         </is>
@@ -6022,18 +5439,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
         <is>
           <t>https://x.com/CardioOnline/status/778987852877135873</t>
         </is>
@@ -6072,20 +5483,15 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Diabetes</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>#Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
         <is>
           <t>https://x.com/NEJM/status/779357545920102401</t>
         </is>
@@ -6122,18 +5528,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
         <is>
           <t>https://x.com/Bob_Barrett_650/status/780154293408059392</t>
         </is>
@@ -6172,20 +5572,15 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#diabetes #health</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>#diabetes #health</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
         <is>
           <t>https://x.com/dalasking1233/status/780357660088696832</t>
         </is>
@@ -6222,18 +5617,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
         <is>
           <t>https://x.com/altebby/status/780698289179983874</t>
         </is>
@@ -6274,20 +5663,15 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#semaglutide #diabetes #biotech</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>#semaglutide #diabetes #biotech</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
         <is>
           <t>https://x.com/MedWatchNews/status/782922267818913792</t>
         </is>
@@ -6326,20 +5710,15 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#GLP1 #Lyxumia #Tanzeum #Eperzan #Trulicity #semaglutidehttp</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>#GLP1 #Lyxumia #Tanzeum #Eperzan #Trulicity #semaglutidehttp</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
         <is>
           <t>https://x.com/fwpharma/status/783615401917808642</t>
         </is>
@@ -6380,20 +5759,15 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Diabetes</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>#Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
         <is>
           <t>https://x.com/medivizor/status/783810517123133440</t>
         </is>
@@ -6434,20 +5808,15 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Diabetes</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>#Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
         <is>
           <t>https://x.com/medivizor/status/783972907089268737</t>
         </is>
@@ -6488,20 +5857,15 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Diabetes</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>#Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
         <is>
           <t>https://x.com/medivizor/status/783993697042100224</t>
         </is>
@@ -6541,20 +5905,15 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#type2diabetes</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>#type2diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
         <is>
           <t>https://x.com/NEJMClinician/status/784080365065502720</t>
         </is>
@@ -6595,20 +5954,15 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Diabetes</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>#Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
         <is>
           <t>https://x.com/medivizor/status/784229638679719936</t>
         </is>
@@ -6649,20 +6003,15 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Diabetes</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>#Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
         <is>
           <t>https://x.com/medivizor/status/784396920974376961</t>
         </is>
@@ -6703,20 +6052,15 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Diabetes</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>#Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
         <is>
           <t>https://x.com/medivizor/status/784500696926281730</t>
         </is>
@@ -6757,20 +6101,15 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#Diabetes</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>#Diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
         <is>
           <t>https://x.com/medivizor/status/784862968836157440</t>
         </is>
@@ -6811,20 +6150,15 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#type2diabetes</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>#type2diabetes</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
         <is>
           <t>https://x.com/NEJMClinician/status/785219613030248452</t>
         </is>
@@ -6863,20 +6197,15 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#SENEFRO16 #t</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>#SENEFRO16 #t</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
         <is>
           <t>https://x.com/ralcazara/status/785370594011410432</t>
         </is>
@@ -6913,18 +6242,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I127" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
         <is>
           <t>https://x.com/syuichiao89/status/785463190121353216</t>
         </is>
@@ -6961,18 +6284,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
         <is>
           <t>https://x.com/T462759/status/785482838883786752</t>
         </is>
@@ -7009,18 +6326,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
         <is>
           <t>https://x.com/Vannyamoto/status/785506087587885057</t>
         </is>
@@ -7057,18 +6368,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
         <is>
           <t>https://x.com/Vannyamoto/status/785510481922363392</t>
         </is>
@@ -7107,18 +6412,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
         <is>
           <t>https://x.com/RichardLehman1/status/785618096220352512</t>
         </is>
@@ -7159,20 +6458,15 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#EASD16</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>#EASD16</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
         <is>
           <t>https://x.com/diaTribeNews/status/790282016935796736</t>
         </is>
@@ -7211,20 +6505,15 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>#liraglutide #dulaglutide #semaglutide #Hanmi</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>#liraglutide #dulaglutide #semaglutide #Hanmi</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
         <is>
           <t>https://x.com/DanielJDrucker/status/792847439438966784</t>
         </is>
@@ -7261,18 +6550,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Semaglutide</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr">
-        <is>
-          <t>Semaglutide</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
         <is>
           <t>https://x.com/CristobMorales/status/793339716397633537</t>
         </is>
